--- a/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_pi_detail.xlsx
+++ b/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_pi_detail.xlsx
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>119.427</v>
+        <v>119.154</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.02229013122415968</v>
+        <v>0.01995326262807851</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>128.293</v>
+        <v>128.296</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.04222754782891269</v>
+        <v>0.04225191924936023</v>
       </c>
       <c r="L41" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>115.283</v>
+        <v>115.794</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.01216888943519145</v>
+        <v>0.01665539917644887</v>
       </c>
       <c r="L61" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>112.389</v>
+        <v>112.918</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>-0.01986622131912408</v>
+        <v>-0.01525286263702719</v>
       </c>
       <c r="L81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>122.378</v>
+        <v>122.412</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>0.01182326288983693</v>
+        <v>0.01210437543407106</v>
       </c>
       <c r="L101" t="n">
         <v>34</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>108.283</v>
+        <v>108.147</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>-0.006823997725334041</v>
+        <v>-0.008071395158997241</v>
       </c>
       <c r="L121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -7644,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>90.824</v>
+        <v>90.801</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>-0.009326017953948051</v>
+        <v>-0.009576893290720867</v>
       </c>
       <c r="L141" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142">
@@ -8668,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>128.222</v>
+        <v>128.011</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>0.03596994425143429</v>
+        <v>0.03426516926557333</v>
       </c>
       <c r="L161" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="162">
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>105.356</v>
+        <v>105.242</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>-0.01271635133488891</v>
+        <v>-0.01378463729817347</v>
       </c>
       <c r="L181" t="n">
         <v>15</v>
@@ -10716,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>107.236</v>
+        <v>107.215</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>0.06967511546019489</v>
+        <v>0.06946564124048638</v>
       </c>
       <c r="L201" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="202">
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>132.916</v>
+        <v>132.493</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -11748,10 +11748,10 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>0.03472811490405192</v>
+        <v>0.03143513292592726</v>
       </c>
       <c r="L221" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222">
@@ -12764,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>132.955</v>
+        <v>132.592</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>0.03388881544670563</v>
+        <v>0.03106604353134212</v>
       </c>
       <c r="L241" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="242">
@@ -13788,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>139.413</v>
+        <v>139.45</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>0.04910939369539546</v>
+        <v>0.04938782574668688</v>
       </c>
       <c r="L261" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="262">
@@ -14812,7 +14812,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>146.028</v>
+        <v>146.163</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>0.09624046603807579</v>
+        <v>0.09725391868356259</v>
       </c>
       <c r="L281" t="n">
         <v>90</v>
@@ -15836,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>112.179</v>
+        <v>112.18</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -15844,10 +15844,10 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>-0.0154036547474854</v>
+        <v>-0.01539487773623316</v>
       </c>
       <c r="L301" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302">
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="I321" t="n">
-        <v>132.862</v>
+        <v>132.576</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="K321" t="n">
-        <v>0.1146421470339019</v>
+        <v>0.1122427577875282</v>
       </c>
       <c r="L321" t="n">
         <v>91</v>
@@ -17884,7 +17884,7 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>144.988</v>
+        <v>145.508</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         </is>
       </c>
       <c r="K341" t="n">
-        <v>0.07747300520945588</v>
+        <v>0.08133736614076703</v>
       </c>
       <c r="L341" t="n">
         <v>89</v>
@@ -18908,7 +18908,7 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>136.183</v>
+        <v>136.184</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -18916,10 +18916,10 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>0.03637664284681486</v>
+        <v>0.03638425302314263</v>
       </c>
       <c r="L361" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="362">
@@ -19932,7 +19932,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>138.333</v>
+        <v>138.334</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -19940,10 +19940,10 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>0.03493087143883189</v>
+        <v>0.0349383528848457</v>
       </c>
       <c r="L381" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="382">
@@ -20956,7 +20956,7 @@
         <v>0</v>
       </c>
       <c r="I401" t="n">
-        <v>100.117</v>
+        <v>100.106</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         </is>
       </c>
       <c r="K401" t="n">
-        <v>-0.004781407185033393</v>
+        <v>-0.004890753295294203</v>
       </c>
       <c r="L401" t="n">
         <v>23</v>
@@ -21980,7 +21980,7 @@
         <v>0</v>
       </c>
       <c r="I421" t="n">
-        <v>137.381</v>
+        <v>137.784</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>-0.145635234049963</v>
+        <v>-0.143128999558455</v>
       </c>
       <c r="L421" t="n">
         <v>1</v>
@@ -23004,7 +23004,7 @@
         <v>0</v>
       </c>
       <c r="I441" t="n">
-        <v>129.14</v>
+        <v>129.08</v>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -23012,10 +23012,10 @@
         </is>
       </c>
       <c r="K441" t="n">
-        <v>0.02734222731358815</v>
+        <v>0.0268649117363946</v>
       </c>
       <c r="L441" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="442">
@@ -24028,7 +24028,7 @@
         <v>0</v>
       </c>
       <c r="I461" t="n">
-        <v>102.916</v>
+        <v>103.48</v>
       </c>
       <c r="J461" t="inlineStr">
         <is>
@@ -24036,10 +24036,10 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>0.006976311849945738</v>
+        <v>0.01249474085887892</v>
       </c>
       <c r="L461" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="462">
@@ -25052,7 +25052,7 @@
         <v>0</v>
       </c>
       <c r="I481" t="n">
-        <v>114.269</v>
+        <v>114.294</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>-0.00468612541047142</v>
+        <v>-0.004468368653479327</v>
       </c>
       <c r="L481" t="n">
         <v>24</v>
@@ -26076,7 +26076,7 @@
         <v>0</v>
       </c>
       <c r="I501" t="n">
-        <v>133.065</v>
+        <v>132.946</v>
       </c>
       <c r="J501" t="inlineStr">
         <is>
@@ -26084,10 +26084,10 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>0.03009026304788742</v>
+        <v>0.02916905355401078</v>
       </c>
       <c r="L501" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="502">
@@ -27100,7 +27100,7 @@
         <v>0</v>
       </c>
       <c r="I521" t="n">
-        <v>105.091</v>
+        <v>105.114</v>
       </c>
       <c r="J521" t="inlineStr">
         <is>
@@ -27108,10 +27108,10 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>-0.01115951711094598</v>
+        <v>-0.01094310151773192</v>
       </c>
       <c r="L521" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="522">
@@ -28124,7 +28124,7 @@
         <v>0</v>
       </c>
       <c r="I541" t="n">
-        <v>138.329</v>
+        <v>138.366</v>
       </c>
       <c r="J541" t="inlineStr">
         <is>
@@ -28132,10 +28132,10 @@
         </is>
       </c>
       <c r="K541" t="n">
-        <v>0.04405549014280119</v>
+        <v>0.04433475228693062</v>
       </c>
       <c r="L541" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="542">
@@ -29148,7 +29148,7 @@
         <v>0</v>
       </c>
       <c r="I561" t="n">
-        <v>115.154</v>
+        <v>115.134</v>
       </c>
       <c r="J561" t="inlineStr">
         <is>
@@ -29156,10 +29156,10 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>0.02558758828296859</v>
+        <v>0.02540946375611175</v>
       </c>
       <c r="L561" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="562">
@@ -30172,7 +30172,7 @@
         <v>0</v>
       </c>
       <c r="I581" t="n">
-        <v>143.24</v>
+        <v>143.684</v>
       </c>
       <c r="J581" t="inlineStr">
         <is>
@@ -30180,10 +30180,10 @@
         </is>
       </c>
       <c r="K581" t="n">
-        <v>0.04859372483565405</v>
+        <v>0.05184404327901482</v>
       </c>
       <c r="L581" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="582">
@@ -31196,7 +31196,7 @@
         <v>0</v>
       </c>
       <c r="I601" t="n">
-        <v>116.725</v>
+        <v>116.787</v>
       </c>
       <c r="J601" t="inlineStr">
         <is>
@@ -31204,10 +31204,10 @@
         </is>
       </c>
       <c r="K601" t="n">
-        <v>0.03658807335375869</v>
+        <v>0.03713867057413078</v>
       </c>
       <c r="L601" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="602">
@@ -32220,7 +32220,7 @@
         <v>0</v>
       </c>
       <c r="I621" t="n">
-        <v>116.255</v>
+        <v>115.959</v>
       </c>
       <c r="J621" t="inlineStr">
         <is>
@@ -32228,10 +32228,10 @@
         </is>
       </c>
       <c r="K621" t="n">
-        <v>0.0004561023046074641</v>
+        <v>-0.002091186038105985</v>
       </c>
       <c r="L621" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="622">
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="I641" t="n">
-        <v>123.376</v>
+        <v>123.402</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="K641" t="n">
-        <v>0.02981536509632399</v>
+        <v>0.03003238623084381</v>
       </c>
       <c r="L641" t="n">
         <v>55</v>
@@ -34268,7 +34268,7 @@
         <v>0</v>
       </c>
       <c r="I661" t="n">
-        <v>137.444</v>
+        <v>137.48</v>
       </c>
       <c r="J661" t="inlineStr">
         <is>
@@ -34276,10 +34276,10 @@
         </is>
       </c>
       <c r="K661" t="n">
-        <v>0.04829458783330276</v>
+        <v>0.04856916224296781</v>
       </c>
       <c r="L661" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="662">
@@ -35292,7 +35292,7 @@
         <v>0</v>
       </c>
       <c r="I681" t="n">
-        <v>122.434</v>
+        <v>122.424</v>
       </c>
       <c r="J681" t="inlineStr">
         <is>
@@ -35300,10 +35300,10 @@
         </is>
       </c>
       <c r="K681" t="n">
-        <v>0.0308582205794441</v>
+        <v>0.03077402352465719</v>
       </c>
       <c r="L681" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="682">
@@ -36316,7 +36316,7 @@
         <v>0</v>
       </c>
       <c r="I701" t="n">
-        <v>154.15</v>
+        <v>154.933</v>
       </c>
       <c r="J701" t="inlineStr">
         <is>
@@ -36324,10 +36324,10 @@
         </is>
       </c>
       <c r="K701" t="n">
-        <v>0.03160740696125885</v>
+        <v>0.03684742382568085</v>
       </c>
       <c r="L701" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="702">
@@ -37340,7 +37340,7 @@
         <v>0</v>
       </c>
       <c r="I721" t="n">
-        <v>122.888</v>
+        <v>122.872</v>
       </c>
       <c r="J721" t="inlineStr">
         <is>
@@ -37348,10 +37348,10 @@
         </is>
       </c>
       <c r="K721" t="n">
-        <v>0.04420236901585572</v>
+        <v>0.04406641401696043</v>
       </c>
       <c r="L721" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="722">
@@ -38364,7 +38364,7 @@
         <v>0</v>
       </c>
       <c r="I741" t="n">
-        <v>107.17</v>
+        <v>107.168</v>
       </c>
       <c r="J741" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         </is>
       </c>
       <c r="K741" t="n">
-        <v>-3.732248493104606e-05</v>
+        <v>-5.598372739656909e-05</v>
       </c>
       <c r="L741" t="n">
         <v>26</v>
@@ -39388,7 +39388,7 @@
         <v>0</v>
       </c>
       <c r="I761" t="n">
-        <v>113.122</v>
+        <v>114.87</v>
       </c>
       <c r="J761" t="inlineStr">
         <is>
@@ -39396,10 +39396,10 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>0.027009360218617</v>
+        <v>0.04287906161765642</v>
       </c>
       <c r="L761" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="762">
@@ -40412,7 +40412,7 @@
         <v>0</v>
       </c>
       <c r="I781" t="n">
-        <v>128.159</v>
+        <v>127.984</v>
       </c>
       <c r="J781" t="inlineStr">
         <is>
@@ -40420,10 +40420,10 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>0.03510132215518547</v>
+        <v>0.03368790030126068</v>
       </c>
       <c r="L781" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="782">
@@ -41436,7 +41436,7 @@
         <v>0</v>
       </c>
       <c r="I801" t="n">
-        <v>111.212</v>
+        <v>111.294</v>
       </c>
       <c r="J801" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>-0.02048653314308857</v>
+        <v>-0.01976430798499185</v>
       </c>
       <c r="L801" t="n">
         <v>12</v>
@@ -42460,7 +42460,7 @@
         <v>0</v>
       </c>
       <c r="I821" t="n">
-        <v>109.87</v>
+        <v>110.187</v>
       </c>
       <c r="J821" t="inlineStr">
         <is>
@@ -42468,10 +42468,10 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>0.01617632097372401</v>
+        <v>0.01910822134460477</v>
       </c>
       <c r="L821" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="822">
@@ -43484,7 +43484,7 @@
         <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>133.597</v>
+        <v>133.027</v>
       </c>
       <c r="J841" t="inlineStr">
         <is>
@@ -43492,10 +43492,10 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>-0.079980166791772</v>
+        <v>-0.08390548925356911</v>
       </c>
       <c r="L841" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="842">
@@ -44508,7 +44508,7 @@
         <v>0</v>
       </c>
       <c r="I861" t="n">
-        <v>120.541</v>
+        <v>120.531</v>
       </c>
       <c r="J861" t="inlineStr">
         <is>
@@ -44516,10 +44516,10 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>0.01675171861161484</v>
+        <v>0.01666736957530257</v>
       </c>
       <c r="L861" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="862">
@@ -45532,7 +45532,7 @@
         <v>0</v>
       </c>
       <c r="I881" t="n">
-        <v>127.028</v>
+        <v>127.03</v>
       </c>
       <c r="J881" t="inlineStr">
         <is>
@@ -45540,10 +45540,10 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>0.02086280056577094</v>
+        <v>0.02087887360164586</v>
       </c>
       <c r="L881" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="882">
@@ -46556,7 +46556,7 @@
         <v>0</v>
       </c>
       <c r="I901" t="n">
-        <v>141.322</v>
+        <v>141.485</v>
       </c>
       <c r="J901" t="inlineStr">
         <is>
@@ -46564,10 +46564,10 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>0.0377207475125747</v>
+        <v>0.03891764878657722</v>
       </c>
       <c r="L901" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="902">
@@ -47580,7 +47580,7 @@
         <v>0</v>
       </c>
       <c r="I921" t="n">
-        <v>119.288</v>
+        <v>119.398</v>
       </c>
       <c r="J921" t="inlineStr">
         <is>
@@ -47588,10 +47588,10 @@
         </is>
       </c>
       <c r="K921" t="n">
-        <v>-0.0004273540083292726</v>
+        <v>0.0004943899312044309</v>
       </c>
       <c r="L921" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="922">
@@ -48604,7 +48604,7 @@
         <v>0</v>
       </c>
       <c r="I941" t="n">
-        <v>130.02</v>
+        <v>130.044</v>
       </c>
       <c r="J941" t="inlineStr">
         <is>
@@ -48612,10 +48612,10 @@
         </is>
       </c>
       <c r="K941" t="n">
-        <v>0.05137182918644423</v>
+        <v>0.05156589874420825</v>
       </c>
       <c r="L941" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="942">
@@ -49628,7 +49628,7 @@
         <v>0</v>
       </c>
       <c r="I961" t="n">
-        <v>132.914</v>
+        <v>133.301</v>
       </c>
       <c r="J961" t="inlineStr">
         <is>
@@ -49636,10 +49636,10 @@
         </is>
       </c>
       <c r="K961" t="n">
-        <v>0.02299770638671239</v>
+        <v>0.02597632498499136</v>
       </c>
       <c r="L961" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="962">
@@ -50652,7 +50652,7 @@
         <v>0</v>
       </c>
       <c r="I981" t="n">
-        <v>121.219</v>
+        <v>121.14</v>
       </c>
       <c r="J981" t="inlineStr">
         <is>
@@ -50660,10 +50660,10 @@
         </is>
       </c>
       <c r="K981" t="n">
-        <v>-0.007629900696678682</v>
+        <v>-0.008276641206375723</v>
       </c>
       <c r="L981" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="982">
@@ -51676,7 +51676,7 @@
         <v>0</v>
       </c>
       <c r="I1001" t="n">
-        <v>131.587</v>
+        <v>128.858</v>
       </c>
       <c r="J1001" t="inlineStr">
         <is>
@@ -51684,10 +51684,10 @@
         </is>
       </c>
       <c r="K1001" t="n">
-        <v>-0.03963011889035672</v>
+        <v>-0.05954735543764633</v>
       </c>
       <c r="L1001" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1002">
@@ -52700,7 +52700,7 @@
         <v>0</v>
       </c>
       <c r="I1021" t="n">
-        <v>129.13</v>
+        <v>129.381</v>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
@@ -52708,10 +52708,10 @@
         </is>
       </c>
       <c r="K1021" t="n">
-        <v>0.02359021513388404</v>
+        <v>0.02557984685384529</v>
       </c>
       <c r="L1021" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1022">
@@ -53724,7 +53724,7 @@
         <v>0</v>
       </c>
       <c r="I1041" t="n">
-        <v>107.247</v>
+        <v>107.354</v>
       </c>
       <c r="J1041" t="inlineStr">
         <is>
@@ -53732,10 +53732,10 @@
         </is>
       </c>
       <c r="K1041" t="n">
-        <v>0.005927871312667143</v>
+        <v>0.006931482436805414</v>
       </c>
       <c r="L1041" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1042">
@@ -54748,7 +54748,7 @@
         <v>0</v>
       </c>
       <c r="I1061" t="n">
-        <v>137.028</v>
+        <v>137.284</v>
       </c>
       <c r="J1061" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         </is>
       </c>
       <c r="K1061" t="n">
-        <v>0.1340185709320223</v>
+        <v>0.1361371799328002</v>
       </c>
       <c r="L1061" t="n">
         <v>92</v>
@@ -55772,7 +55772,7 @@
         <v>0</v>
       </c>
       <c r="I1081" t="n">
-        <v>112.485</v>
+        <v>112.484</v>
       </c>
       <c r="J1081" t="inlineStr">
         <is>
@@ -55780,10 +55780,10 @@
         </is>
       </c>
       <c r="K1081" t="n">
-        <v>0.005173985309098628</v>
+        <v>0.005165049237753072</v>
       </c>
       <c r="L1081" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1082">
@@ -56796,7 +56796,7 @@
         <v>0</v>
       </c>
       <c r="I1101" t="n">
-        <v>138.892</v>
+        <v>139.119</v>
       </c>
       <c r="J1101" t="inlineStr">
         <is>
@@ -56804,10 +56804,10 @@
         </is>
       </c>
       <c r="K1101" t="n">
-        <v>0.05095416092858551</v>
+        <v>0.05267180193404863</v>
       </c>
       <c r="L1101" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1102">
@@ -57820,7 +57820,7 @@
         <v>0</v>
       </c>
       <c r="I1121" t="n">
-        <v>113.428</v>
+        <v>113.378</v>
       </c>
       <c r="J1121" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         </is>
       </c>
       <c r="K1121" t="n">
-        <v>0.02005431752369646</v>
+        <v>0.01960466914872572</v>
       </c>
       <c r="L1121" t="n">
         <v>41</v>
@@ -58844,7 +58844,7 @@
         <v>0</v>
       </c>
       <c r="I1141" t="n">
-        <v>127.054</v>
+        <v>127.568</v>
       </c>
       <c r="J1141" t="inlineStr">
         <is>
@@ -58852,10 +58852,10 @@
         </is>
       </c>
       <c r="K1141" t="n">
-        <v>-0.01196799203689147</v>
+        <v>-0.0079708848848693</v>
       </c>
       <c r="L1141" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1142">
@@ -59868,7 +59868,7 @@
         <v>0</v>
       </c>
       <c r="I1161" t="n">
-        <v>137.139</v>
+        <v>137.175</v>
       </c>
       <c r="J1161" t="inlineStr">
         <is>
@@ -59876,10 +59876,10 @@
         </is>
       </c>
       <c r="K1161" t="n">
-        <v>0.04957868070809202</v>
+        <v>0.04985420286083841</v>
       </c>
       <c r="L1161" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1162">
@@ -60892,7 +60892,7 @@
         <v>0</v>
       </c>
       <c r="I1181" t="n">
-        <v>124.443</v>
+        <v>124.482</v>
       </c>
       <c r="J1181" t="inlineStr">
         <is>
@@ -60900,10 +60900,10 @@
         </is>
       </c>
       <c r="K1181" t="n">
-        <v>0.02439084622983212</v>
+        <v>0.02471188673032598</v>
       </c>
       <c r="L1181" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1182">
@@ -62940,7 +62940,7 @@
         <v>0</v>
       </c>
       <c r="I1221" t="n">
-        <v>108.655</v>
+        <v>108.691</v>
       </c>
       <c r="J1221" t="inlineStr">
         <is>
@@ -62948,10 +62948,10 @@
         </is>
       </c>
       <c r="K1221" t="n">
-        <v>0.008539471852230029</v>
+        <v>0.008873625098621662</v>
       </c>
       <c r="L1221" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1222">
@@ -63964,7 +63964,7 @@
         <v>0</v>
       </c>
       <c r="I1241" t="n">
-        <v>110.487</v>
+        <v>110.481</v>
       </c>
       <c r="J1241" t="inlineStr">
         <is>
@@ -63972,10 +63972,10 @@
         </is>
       </c>
       <c r="K1241" t="n">
-        <v>0.02023158750092335</v>
+        <v>0.02017618379256847</v>
       </c>
       <c r="L1241" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1242">
@@ -64988,7 +64988,7 @@
         <v>0</v>
       </c>
       <c r="I1261" t="n">
-        <v>138.404</v>
+        <v>138.405</v>
       </c>
       <c r="J1261" t="inlineStr">
         <is>
@@ -64996,10 +64996,10 @@
         </is>
       </c>
       <c r="K1261" t="n">
-        <v>0.03488911154645646</v>
+        <v>0.03489658885283164</v>
       </c>
       <c r="L1261" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1262">
@@ -66012,7 +66012,7 @@
         <v>0</v>
       </c>
       <c r="I1281" t="n">
-        <v>113.03</v>
+        <v>112.966</v>
       </c>
       <c r="J1281" t="inlineStr">
         <is>
@@ -66020,10 +66020,10 @@
         </is>
       </c>
       <c r="K1281" t="n">
-        <v>0.01486882037100234</v>
+        <v>0.01429417997019056</v>
       </c>
       <c r="L1281" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1282">
@@ -67036,7 +67036,7 @@
         <v>0</v>
       </c>
       <c r="I1301" t="n">
-        <v>132.333</v>
+        <v>132.229</v>
       </c>
       <c r="J1301" t="inlineStr">
         <is>
@@ -67044,7 +67044,7 @@
         </is>
       </c>
       <c r="K1301" t="n">
-        <v>0.02237381892349166</v>
+        <v>0.02157033923839391</v>
       </c>
       <c r="L1301" t="n">
         <v>45</v>
@@ -68060,7 +68060,7 @@
         <v>0</v>
       </c>
       <c r="I1321" t="n">
-        <v>147.373</v>
+        <v>146.829</v>
       </c>
       <c r="J1321" t="inlineStr">
         <is>
@@ -68068,10 +68068,10 @@
         </is>
       </c>
       <c r="K1321" t="n">
-        <v>0.07302884020299549</v>
+        <v>0.06906795395469745</v>
       </c>
       <c r="L1321" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1322">
@@ -69084,7 +69084,7 @@
         <v>0</v>
       </c>
       <c r="I1341" t="n">
-        <v>120.816</v>
+        <v>120.823</v>
       </c>
       <c r="J1341" t="inlineStr">
         <is>
@@ -69092,10 +69092,10 @@
         </is>
       </c>
       <c r="K1341" t="n">
-        <v>0.02313607262626594</v>
+        <v>0.02319535246095983</v>
       </c>
       <c r="L1341" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1342">
@@ -70108,7 +70108,7 @@
         <v>0</v>
       </c>
       <c r="I1361" t="n">
-        <v>101.118</v>
+        <v>101.125</v>
       </c>
       <c r="J1361" t="inlineStr">
         <is>
@@ -70116,7 +70116,7 @@
         </is>
       </c>
       <c r="K1361" t="n">
-        <v>-0.02092390515012732</v>
+        <v>-0.02085612757675803</v>
       </c>
       <c r="L1361" t="n">
         <v>11</v>
@@ -71132,7 +71132,7 @@
         <v>0</v>
       </c>
       <c r="I1381" t="n">
-        <v>99.761</v>
+        <v>99.992</v>
       </c>
       <c r="J1381" t="inlineStr">
         <is>
@@ -71140,10 +71140,10 @@
         </is>
       </c>
       <c r="K1381" t="n">
-        <v>-0.01074916951757654</v>
+        <v>-0.008458525459864141</v>
       </c>
       <c r="L1381" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1382">
@@ -72156,7 +72156,7 @@
         <v>0</v>
       </c>
       <c r="I1401" t="n">
-        <v>124.259</v>
+        <v>123.949</v>
       </c>
       <c r="J1401" t="inlineStr">
         <is>
@@ -72164,10 +72164,10 @@
         </is>
       </c>
       <c r="K1401" t="n">
-        <v>0.03684820974107783</v>
+        <v>0.03426149211885554</v>
       </c>
       <c r="L1401" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1402">
@@ -73180,7 +73180,7 @@
         <v>0</v>
       </c>
       <c r="I1421" t="n">
-        <v>129.435</v>
+        <v>129.481</v>
       </c>
       <c r="J1421" t="inlineStr">
         <is>
@@ -73188,10 +73188,10 @@
         </is>
       </c>
       <c r="K1421" t="n">
-        <v>0.0381376323387872</v>
+        <v>0.03850657683670189</v>
       </c>
       <c r="L1421" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1422">
@@ -74204,7 +74204,7 @@
         <v>0</v>
       </c>
       <c r="I1441" t="n">
-        <v>134.898</v>
+        <v>134.534</v>
       </c>
       <c r="J1441" t="inlineStr">
         <is>
@@ -74212,10 +74212,10 @@
         </is>
       </c>
       <c r="K1441" t="n">
-        <v>0.04868814863761806</v>
+        <v>0.04585843666187284</v>
       </c>
       <c r="L1441" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1442">
@@ -75228,7 +75228,7 @@
         <v>0</v>
       </c>
       <c r="I1461" t="n">
-        <v>102.483</v>
+        <v>102.484</v>
       </c>
       <c r="J1461" t="inlineStr">
         <is>
@@ -75236,7 +75236,7 @@
         </is>
       </c>
       <c r="K1461" t="n">
-        <v>-0.02428737361235411</v>
+        <v>-0.02427785288573236</v>
       </c>
       <c r="L1461" t="n">
         <v>7</v>
@@ -76252,7 +76252,7 @@
         <v>0</v>
       </c>
       <c r="I1481" t="n">
-        <v>112.518</v>
+        <v>112.517</v>
       </c>
       <c r="J1481" t="inlineStr">
         <is>
@@ -76260,7 +76260,7 @@
         </is>
       </c>
       <c r="K1481" t="n">
-        <v>0.02280722486342035</v>
+        <v>0.02279813469807013</v>
       </c>
       <c r="L1481" t="n">
         <v>46</v>
@@ -77276,7 +77276,7 @@
         <v>0</v>
       </c>
       <c r="I1501" t="n">
-        <v>37.484</v>
+        <v>38.135</v>
       </c>
       <c r="J1501" t="inlineStr">
         <is>
@@ -77284,10 +77284,10 @@
         </is>
       </c>
       <c r="K1501" t="n">
-        <v>-0.09202335101615677</v>
+        <v>-0.07625414819659426</v>
       </c>
       <c r="L1501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1502">
@@ -78300,7 +78300,7 @@
         <v>0</v>
       </c>
       <c r="I1521" t="n">
-        <v>79.733</v>
+        <v>79.73399999999999</v>
       </c>
       <c r="J1521" t="inlineStr">
         <is>
@@ -78308,7 +78308,7 @@
         </is>
       </c>
       <c r="K1521" t="n">
-        <v>-0.02211293171114592</v>
+        <v>-0.02210066718995296</v>
       </c>
       <c r="L1521" t="n">
         <v>9</v>
@@ -79324,7 +79324,7 @@
         <v>0</v>
       </c>
       <c r="I1541" t="n">
-        <v>117.087</v>
+        <v>117.072</v>
       </c>
       <c r="J1541" t="inlineStr">
         <is>
@@ -79332,7 +79332,7 @@
         </is>
       </c>
       <c r="K1541" t="n">
-        <v>0.02685376014032004</v>
+        <v>0.02672221004165753</v>
       </c>
       <c r="L1541" t="n">
         <v>52</v>
@@ -80348,7 +80348,7 @@
         <v>0</v>
       </c>
       <c r="I1561" t="n">
-        <v>138.348</v>
+        <v>138.384</v>
       </c>
       <c r="J1561" t="inlineStr">
         <is>
@@ -80356,10 +80356,10 @@
         </is>
       </c>
       <c r="K1561" t="n">
-        <v>0.04408069007675075</v>
+        <v>0.04435237383685386</v>
       </c>
       <c r="L1561" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1562">
@@ -81372,7 +81372,7 @@
         <v>0</v>
       </c>
       <c r="I1581" t="n">
-        <v>130.101</v>
+        <v>130.23</v>
       </c>
       <c r="J1581" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         </is>
       </c>
       <c r="K1581" t="n">
-        <v>0.01376086024856815</v>
+        <v>0.01476604199945442</v>
       </c>
       <c r="L1581" t="n">
         <v>37</v>
@@ -82396,7 +82396,7 @@
         <v>0</v>
       </c>
       <c r="I1601" t="n">
-        <v>132.019</v>
+        <v>132.02</v>
       </c>
       <c r="J1601" t="inlineStr">
         <is>
@@ -82404,7 +82404,7 @@
         </is>
       </c>
       <c r="K1601" t="n">
-        <v>0.06248440706611413</v>
+        <v>0.06249245503199075</v>
       </c>
       <c r="L1601" t="n">
         <v>84</v>
@@ -84444,7 +84444,7 @@
         <v>0</v>
       </c>
       <c r="I1641" t="n">
-        <v>123.314</v>
+        <v>122.966</v>
       </c>
       <c r="J1641" t="inlineStr">
         <is>
@@ -84452,7 +84452,7 @@
         </is>
       </c>
       <c r="K1641" t="n">
-        <v>-0.02574798732747108</v>
+        <v>-0.02849738885860331</v>
       </c>
       <c r="L1641" t="n">
         <v>6</v>
@@ -85468,7 +85468,7 @@
         <v>0</v>
       </c>
       <c r="I1661" t="n">
-        <v>88.148</v>
+        <v>88.11499999999999</v>
       </c>
       <c r="J1661" t="inlineStr">
         <is>
@@ -85476,10 +85476,10 @@
         </is>
       </c>
       <c r="K1661" t="n">
-        <v>-0.04477676636324235</v>
+        <v>-0.04513437364542705</v>
       </c>
       <c r="L1661" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1662">
@@ -86492,7 +86492,7 @@
         <v>0</v>
       </c>
       <c r="I1681" t="n">
-        <v>133.581</v>
+        <v>133.274</v>
       </c>
       <c r="J1681" t="inlineStr">
         <is>
@@ -86500,10 +86500,10 @@
         </is>
       </c>
       <c r="K1681" t="n">
-        <v>0.03915269004574151</v>
+        <v>0.03676447708249064</v>
       </c>
       <c r="L1681" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1682">
@@ -87516,7 +87516,7 @@
         <v>0</v>
       </c>
       <c r="I1701" t="n">
-        <v>71.34699999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="J1701" t="inlineStr">
         <is>
@@ -87524,10 +87524,10 @@
         </is>
       </c>
       <c r="K1701" t="n">
-        <v>-0.009908272158310472</v>
+        <v>-0.01028295471891894</v>
       </c>
       <c r="L1701" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1702">
@@ -88540,7 +88540,7 @@
         <v>0</v>
       </c>
       <c r="I1721" t="n">
-        <v>112.779</v>
+        <v>112.749</v>
       </c>
       <c r="J1721" t="inlineStr">
         <is>
@@ -88548,10 +88548,10 @@
         </is>
       </c>
       <c r="K1721" t="n">
-        <v>0.01192462987886933</v>
+        <v>0.01165545087483166</v>
       </c>
       <c r="L1721" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1722">
@@ -89564,7 +89564,7 @@
         <v>0</v>
       </c>
       <c r="I1741" t="n">
-        <v>148.281</v>
+        <v>148.28</v>
       </c>
       <c r="J1741" t="inlineStr">
         <is>
@@ -89572,7 +89572,7 @@
         </is>
       </c>
       <c r="K1741" t="n">
-        <v>0.05907435183201204</v>
+        <v>0.05906720948503685</v>
       </c>
       <c r="L1741" t="n">
         <v>83</v>
@@ -90588,7 +90588,7 @@
         <v>0</v>
       </c>
       <c r="I1761" t="n">
-        <v>98.923</v>
+        <v>98.962</v>
       </c>
       <c r="J1761" t="inlineStr">
         <is>
@@ -90596,7 +90596,7 @@
         </is>
       </c>
       <c r="K1761" t="n">
-        <v>-0.02410078330012033</v>
+        <v>-0.02371603890850971</v>
       </c>
       <c r="L1761" t="n">
         <v>8</v>
@@ -91612,7 +91612,7 @@
         <v>0</v>
       </c>
       <c r="I1781" t="n">
-        <v>98.322</v>
+        <v>99.086</v>
       </c>
       <c r="J1781" t="inlineStr">
         <is>
@@ -91620,10 +91620,10 @@
         </is>
       </c>
       <c r="K1781" t="n">
-        <v>0.003050304520367808</v>
+        <v>0.01084439366271184</v>
       </c>
       <c r="L1781" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1782">
@@ -92636,7 +92636,7 @@
         <v>0</v>
       </c>
       <c r="I1801" t="n">
-        <v>113.129</v>
+        <v>113.13</v>
       </c>
       <c r="J1801" t="inlineStr">
         <is>
@@ -92644,7 +92644,7 @@
         </is>
       </c>
       <c r="K1801" t="n">
-        <v>-0.021815446339017</v>
+        <v>-0.0218067997094733</v>
       </c>
       <c r="L1801" t="n">
         <v>10</v>
@@ -93660,7 +93660,7 @@
         <v>0</v>
       </c>
       <c r="I1821" t="n">
-        <v>134.573</v>
+        <v>134.393</v>
       </c>
       <c r="J1821" t="inlineStr">
         <is>
@@ -93668,10 +93668,10 @@
         </is>
       </c>
       <c r="K1821" t="n">
-        <v>0.05142549085482573</v>
+        <v>0.05001914197091994</v>
       </c>
       <c r="L1821" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1822">

--- a/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_pi_detail.xlsx
+++ b/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_pi_detail.xlsx
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>120.223</v>
+        <v>120.231</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.00823542237988617</v>
+        <v>0.008302513397237421</v>
       </c>
       <c r="L22" t="n">
         <v>31</v>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>131.041</v>
+        <v>129.612</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.04307922533809871</v>
+        <v>0.03170446314147202</v>
       </c>
       <c r="L43" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
@@ -3704,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>116.226</v>
+        <v>116.225</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.01318060568021351</v>
+        <v>0.01317188834841421</v>
       </c>
       <c r="L64" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>109.754</v>
+        <v>109.753</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>-0.0455924937172274</v>
+        <v>-0.04560118959625037</v>
       </c>
       <c r="L85" t="n">
         <v>6</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>126.026</v>
+        <v>126.021</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>0.0338643784147401</v>
+        <v>0.03382336051452861</v>
       </c>
       <c r="L106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107">
@@ -6932,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>107.934</v>
+        <v>107.932</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>-0.02691153003543123</v>
+        <v>-0.02692956121133439</v>
       </c>
       <c r="L127" t="n">
         <v>8</v>
@@ -8008,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>90.95</v>
+        <v>90.93600000000001</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>-0.01541559313226659</v>
+        <v>-0.01556715092991523</v>
       </c>
       <c r="L148" t="n">
         <v>12</v>
@@ -10160,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>105.473</v>
+        <v>105.475</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>-0.01043298775625079</v>
+        <v>-0.01041422338978282</v>
       </c>
       <c r="L190" t="n">
         <v>13</v>
@@ -11236,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>110.547</v>
+        <v>110.543</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>0.105436836894893</v>
+        <v>0.1053968380948571</v>
       </c>
       <c r="L211" t="n">
         <v>90</v>
@@ -12312,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>133.803</v>
+        <v>133.794</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>0.01643889728727799</v>
+        <v>0.0163705284907969</v>
       </c>
       <c r="L232" t="n">
         <v>41</v>
@@ -13388,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>135.398</v>
+        <v>135.406</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>0.02515994699981072</v>
+        <v>0.02522051864470964</v>
       </c>
       <c r="L253" t="n">
         <v>51</v>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="I295" t="n">
-        <v>157.555</v>
+        <v>155.522</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>0.1547651331364202</v>
+        <v>0.1398647014416698</v>
       </c>
       <c r="L295" t="n">
         <v>92</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>113.12</v>
+        <v>113.124</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>-0.007188056767217454</v>
+        <v>-0.007152950262859892</v>
       </c>
       <c r="L316" t="n">
         <v>16</v>
@@ -17692,7 +17692,7 @@
         <v>0</v>
       </c>
       <c r="I337" t="n">
-        <v>133.028</v>
+        <v>133.206</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         </is>
       </c>
       <c r="K337" t="n">
-        <v>0.09440326441963576</v>
+        <v>0.09586764621194033</v>
       </c>
       <c r="L337" t="n">
         <v>89</v>
@@ -18768,7 +18768,7 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>150.037</v>
+        <v>149.47</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>0.08470936957779074</v>
+        <v>0.08061017929438985</v>
       </c>
       <c r="L358" t="n">
         <v>88</v>
@@ -19855,7 +19855,7 @@
         <v>0.03681643868707929</v>
       </c>
       <c r="L379" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="380">
@@ -20920,7 +20920,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>139.512</v>
+        <v>139.515</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -20928,10 +20928,10 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>0.03465614547719875</v>
+        <v>0.03467839423312236</v>
       </c>
       <c r="L400" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="401">
@@ -21996,7 +21996,7 @@
         <v>0</v>
       </c>
       <c r="I421" t="n">
-        <v>100.746</v>
+        <v>101.18</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -22004,10 +22004,10 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>-0.02304067027404433</v>
+        <v>-0.01883206299334761</v>
       </c>
       <c r="L421" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="422">
@@ -23072,7 +23072,7 @@
         <v>0</v>
       </c>
       <c r="I442" t="n">
-        <v>144.773</v>
+        <v>144.752</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         </is>
       </c>
       <c r="K442" t="n">
-        <v>-0.04678724510959376</v>
+        <v>-0.0469255130729066</v>
       </c>
       <c r="L442" t="n">
         <v>5</v>
@@ -25224,7 +25224,7 @@
         <v>0</v>
       </c>
       <c r="I484" t="n">
-        <v>102.761</v>
+        <v>102.76</v>
       </c>
       <c r="J484" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>0.008192217883562503</v>
+        <v>0.008182406844181145</v>
       </c>
       <c r="L484" t="n">
         <v>30</v>
@@ -26300,7 +26300,7 @@
         <v>0</v>
       </c>
       <c r="I505" t="n">
-        <v>114.93</v>
+        <v>114.931</v>
       </c>
       <c r="J505" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>0.002363530119746438</v>
+        <v>0.002372251633103284</v>
       </c>
       <c r="L505" t="n">
         <v>26</v>
@@ -27376,7 +27376,7 @@
         <v>0</v>
       </c>
       <c r="I526" t="n">
-        <v>141.809</v>
+        <v>141.773</v>
       </c>
       <c r="J526" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>0.05984215482578747</v>
+        <v>0.0595731005515614</v>
       </c>
       <c r="L526" t="n">
         <v>86</v>
@@ -29539,7 +29539,7 @@
         <v>0.04134758066320177</v>
       </c>
       <c r="L568" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="569">
@@ -31680,7 +31680,7 @@
         <v>0</v>
       </c>
       <c r="I610" t="n">
-        <v>145.523</v>
+        <v>145.524</v>
       </c>
       <c r="J610" t="inlineStr">
         <is>
@@ -31688,10 +31688,10 @@
         </is>
       </c>
       <c r="K610" t="n">
-        <v>0.05148195783176068</v>
+        <v>0.05148918336970199</v>
       </c>
       <c r="L610" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="611">
@@ -32756,7 +32756,7 @@
         <v>0</v>
       </c>
       <c r="I631" t="n">
-        <v>117.146</v>
+        <v>117.184</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         </is>
       </c>
       <c r="K631" t="n">
-        <v>0.0223056113098874</v>
+        <v>0.0226372283794396</v>
       </c>
       <c r="L631" t="n">
         <v>46</v>
@@ -33832,7 +33832,7 @@
         <v>0</v>
       </c>
       <c r="I652" t="n">
-        <v>116.657</v>
+        <v>116.656</v>
       </c>
       <c r="J652" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         </is>
       </c>
       <c r="K652" t="n">
-        <v>0.001760381959949209</v>
+        <v>0.001751794730876277</v>
       </c>
       <c r="L652" t="n">
         <v>25</v>
@@ -34908,7 +34908,7 @@
         <v>0</v>
       </c>
       <c r="I673" t="n">
-        <v>124.113</v>
+        <v>124.473</v>
       </c>
       <c r="J673" t="inlineStr">
         <is>
@@ -34916,10 +34916,10 @@
         </is>
       </c>
       <c r="K673" t="n">
-        <v>0.0234182381898691</v>
+        <v>0.0263867472561905</v>
       </c>
       <c r="L673" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="674">
@@ -37060,7 +37060,7 @@
         <v>0</v>
       </c>
       <c r="I715" t="n">
-        <v>123.114</v>
+        <v>123.499</v>
       </c>
       <c r="J715" t="inlineStr">
         <is>
@@ -37068,10 +37068,10 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>0.02392774270815146</v>
+        <v>0.02712975207298918</v>
       </c>
       <c r="L715" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="716">
@@ -38136,7 +38136,7 @@
         <v>0</v>
       </c>
       <c r="I736" t="n">
-        <v>159.066</v>
+        <v>157.964</v>
       </c>
       <c r="J736" t="inlineStr">
         <is>
@@ -38144,10 +38144,10 @@
         </is>
       </c>
       <c r="K736" t="n">
-        <v>0.05465346797239135</v>
+        <v>0.0473468900631866</v>
       </c>
       <c r="L736" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="737">
@@ -39212,7 +39212,7 @@
         <v>0</v>
       </c>
       <c r="I757" t="n">
-        <v>123.503</v>
+        <v>123.462</v>
       </c>
       <c r="J757" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         </is>
       </c>
       <c r="K757" t="n">
-        <v>0.03178833397383429</v>
+        <v>0.03144580527661289</v>
       </c>
       <c r="L757" t="n">
         <v>58</v>
@@ -40288,7 +40288,7 @@
         <v>0</v>
       </c>
       <c r="I778" t="n">
-        <v>108.988</v>
+        <v>108.984</v>
       </c>
       <c r="J778" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         </is>
       </c>
       <c r="K778" t="n">
-        <v>-0.007603143239576338</v>
+        <v>-0.00763956548264022</v>
       </c>
       <c r="L778" t="n">
         <v>14</v>
@@ -41364,7 +41364,7 @@
         <v>0</v>
       </c>
       <c r="I799" t="n">
-        <v>113.551</v>
+        <v>113.545</v>
       </c>
       <c r="J799" t="inlineStr">
         <is>
@@ -41372,10 +41372,10 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>0.05018265895953755</v>
+        <v>0.05012716763005787</v>
       </c>
       <c r="L799" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="800">
@@ -42440,7 +42440,7 @@
         <v>0</v>
       </c>
       <c r="I820" t="n">
-        <v>128.564</v>
+        <v>128.505</v>
       </c>
       <c r="J820" t="inlineStr">
         <is>
@@ -42448,10 +42448,10 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>0.025280316442573</v>
+        <v>0.02480979951193829</v>
       </c>
       <c r="L820" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="821">
@@ -45668,7 +45668,7 @@
         <v>0</v>
       </c>
       <c r="I883" t="n">
-        <v>135.366</v>
+        <v>135.377</v>
       </c>
       <c r="J883" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>-0.04784480333126995</v>
+        <v>-0.047767430082719</v>
       </c>
       <c r="L883" t="n">
         <v>4</v>
@@ -46744,7 +46744,7 @@
         <v>0</v>
       </c>
       <c r="I904" t="n">
-        <v>121.392</v>
+        <v>121.381</v>
       </c>
       <c r="J904" t="inlineStr">
         <is>
@@ -46752,10 +46752,10 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>0.02922548645555123</v>
+        <v>0.02913222264614879</v>
       </c>
       <c r="L904" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="905">
@@ -47820,7 +47820,7 @@
         <v>0</v>
       </c>
       <c r="I925" t="n">
-        <v>126.512</v>
+        <v>126.514</v>
       </c>
       <c r="J925" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         </is>
       </c>
       <c r="K925" t="n">
-        <v>0.006740142442207331</v>
+        <v>0.006756057772649315</v>
       </c>
       <c r="L925" t="n">
         <v>28</v>
@@ -48896,7 +48896,7 @@
         <v>0</v>
       </c>
       <c r="I946" t="n">
-        <v>142.722</v>
+        <v>142.723</v>
       </c>
       <c r="J946" t="inlineStr">
         <is>
@@ -48904,10 +48904,10 @@
         </is>
       </c>
       <c r="K946" t="n">
-        <v>0.03871094517586959</v>
+        <v>0.03871822303734285</v>
       </c>
       <c r="L946" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="947">
@@ -49972,7 +49972,7 @@
         <v>0</v>
       </c>
       <c r="I967" t="n">
-        <v>120.277</v>
+        <v>120.278</v>
       </c>
       <c r="J967" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         </is>
       </c>
       <c r="K967" t="n">
-        <v>0.009196096693264932</v>
+        <v>0.009204487292437724</v>
       </c>
       <c r="L967" t="n">
         <v>33</v>
@@ -51059,7 +51059,7 @@
         <v>0.05277886606593141</v>
       </c>
       <c r="L988" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="989">
@@ -52124,7 +52124,7 @@
         <v>0</v>
       </c>
       <c r="I1009" t="n">
-        <v>134.517</v>
+        <v>134.51</v>
       </c>
       <c r="J1009" t="inlineStr">
         <is>
@@ -52132,10 +52132,10 @@
         </is>
       </c>
       <c r="K1009" t="n">
-        <v>0.03428470374755888</v>
+        <v>0.03423088160666787</v>
       </c>
       <c r="L1009" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1010">
@@ -53200,7 +53200,7 @@
         <v>0</v>
       </c>
       <c r="I1030" t="n">
-        <v>121.65</v>
+        <v>121.651</v>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         </is>
       </c>
       <c r="K1030" t="n">
-        <v>-0.003269178772460246</v>
+        <v>-0.00326098534195296</v>
       </c>
       <c r="L1030" t="n">
         <v>18</v>
@@ -54276,7 +54276,7 @@
         <v>0</v>
       </c>
       <c r="I1051" t="n">
-        <v>133.383</v>
+        <v>133.38</v>
       </c>
       <c r="J1051" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         </is>
       </c>
       <c r="K1051" t="n">
-        <v>-0.0007566449911600159</v>
+        <v>-0.00077911959485788</v>
       </c>
       <c r="L1051" t="n">
         <v>21</v>
@@ -55352,7 +55352,7 @@
         <v>0</v>
       </c>
       <c r="I1072" t="n">
-        <v>130.228</v>
+        <v>130.428</v>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         </is>
       </c>
       <c r="K1072" t="n">
-        <v>0.02036371044198426</v>
+        <v>0.02193075241520348</v>
       </c>
       <c r="L1072" t="n">
         <v>45</v>
@@ -56428,7 +56428,7 @@
         <v>0</v>
       </c>
       <c r="I1093" t="n">
-        <v>106.626</v>
+        <v>106.627</v>
       </c>
       <c r="J1093" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         </is>
       </c>
       <c r="K1093" t="n">
-        <v>-0.0006841676116926543</v>
+        <v>-0.0006747954526284961</v>
       </c>
       <c r="L1093" t="n">
         <v>22</v>
@@ -57504,7 +57504,7 @@
         <v>0</v>
       </c>
       <c r="I1114" t="n">
-        <v>142.28</v>
+        <v>142.26</v>
       </c>
       <c r="J1114" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         </is>
       </c>
       <c r="K1114" t="n">
-        <v>0.1208798134492972</v>
+        <v>0.120722253734165</v>
       </c>
       <c r="L1114" t="n">
         <v>91</v>
@@ -58580,7 +58580,7 @@
         <v>0</v>
       </c>
       <c r="I1135" t="n">
-        <v>112.877</v>
+        <v>112.876</v>
       </c>
       <c r="J1135" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         </is>
       </c>
       <c r="K1135" t="n">
-        <v>0.003957947915184334</v>
+        <v>0.00394905365020648</v>
       </c>
       <c r="L1135" t="n">
         <v>27</v>
@@ -59656,7 +59656,7 @@
         <v>0</v>
       </c>
       <c r="I1156" t="n">
-        <v>140.81</v>
+        <v>140.814</v>
       </c>
       <c r="J1156" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         </is>
       </c>
       <c r="K1156" t="n">
-        <v>0.04161735116581844</v>
+        <v>0.04164694046632733</v>
       </c>
       <c r="L1156" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1157">
@@ -60732,7 +60732,7 @@
         <v>0</v>
       </c>
       <c r="I1177" t="n">
-        <v>113.305</v>
+        <v>113.449</v>
       </c>
       <c r="J1177" t="inlineStr">
         <is>
@@ -60740,10 +60740,10 @@
         </is>
       </c>
       <c r="K1177" t="n">
-        <v>0.01204937654078386</v>
+        <v>0.01333559612704982</v>
       </c>
       <c r="L1177" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1178">
@@ -61808,7 +61808,7 @@
         <v>0</v>
       </c>
       <c r="I1198" t="n">
-        <v>127.753</v>
+        <v>127.759</v>
       </c>
       <c r="J1198" t="inlineStr">
         <is>
@@ -61816,7 +61816,7 @@
         </is>
       </c>
       <c r="K1198" t="n">
-        <v>-0.0003521181865131506</v>
+        <v>-0.0003051690949780195</v>
       </c>
       <c r="L1198" t="n">
         <v>23</v>
@@ -63960,7 +63960,7 @@
         <v>0</v>
       </c>
       <c r="I1240" t="n">
-        <v>125.584</v>
+        <v>125.57</v>
       </c>
       <c r="J1240" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         </is>
       </c>
       <c r="K1240" t="n">
-        <v>0.02511693209367616</v>
+        <v>0.02500265290962966</v>
       </c>
       <c r="L1240" t="n">
         <v>50</v>
@@ -65036,7 +65036,7 @@
         <v>0</v>
       </c>
       <c r="I1261" t="n">
-        <v>145.513</v>
+        <v>145.516</v>
       </c>
       <c r="J1261" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         </is>
       </c>
       <c r="K1261" t="n">
-        <v>0.05936269192408217</v>
+        <v>0.05938453250242048</v>
       </c>
       <c r="L1261" t="n">
         <v>85</v>
@@ -66112,7 +66112,7 @@
         <v>0</v>
       </c>
       <c r="I1282" t="n">
-        <v>110.283</v>
+        <v>110.281</v>
       </c>
       <c r="J1282" t="inlineStr">
         <is>
@@ -66120,10 +66120,10 @@
         </is>
       </c>
       <c r="K1282" t="n">
-        <v>0.02762817048398225</v>
+        <v>0.02760953428129498</v>
       </c>
       <c r="L1282" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1283">
@@ -67188,7 +67188,7 @@
         <v>0</v>
       </c>
       <c r="I1303" t="n">
-        <v>110.178</v>
+        <v>110.413</v>
       </c>
       <c r="J1303" t="inlineStr">
         <is>
@@ -67196,7 +67196,7 @@
         </is>
       </c>
       <c r="K1303" t="n">
-        <v>0.01000119170936964</v>
+        <v>0.01215543556977461</v>
       </c>
       <c r="L1303" t="n">
         <v>34</v>
@@ -68264,7 +68264,7 @@
         <v>0</v>
       </c>
       <c r="I1324" t="n">
-        <v>139.584</v>
+        <v>139.587</v>
       </c>
       <c r="J1324" t="inlineStr">
         <is>
@@ -68272,10 +68272,10 @@
         </is>
       </c>
       <c r="K1324" t="n">
-        <v>0.03459930623499075</v>
+        <v>0.03462154229298231</v>
       </c>
       <c r="L1324" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1325">
@@ -69340,7 +69340,7 @@
         <v>0</v>
       </c>
       <c r="I1345" t="n">
-        <v>113.354</v>
+        <v>113.413</v>
       </c>
       <c r="J1345" t="inlineStr">
         <is>
@@ -69348,10 +69348,10 @@
         </is>
       </c>
       <c r="K1345" t="n">
-        <v>0.01295753503002572</v>
+        <v>0.01348477266228199</v>
       </c>
       <c r="L1345" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1346">
@@ -70416,7 +70416,7 @@
         <v>0</v>
       </c>
       <c r="I1366" t="n">
-        <v>133.464</v>
+        <v>133.465</v>
       </c>
       <c r="J1366" t="inlineStr">
         <is>
@@ -70424,10 +70424,10 @@
         </is>
       </c>
       <c r="K1366" t="n">
-        <v>0.03468485929141796</v>
+        <v>0.03469261183037431</v>
       </c>
       <c r="L1366" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1367">
@@ -71492,7 +71492,7 @@
         <v>0</v>
       </c>
       <c r="I1387" t="n">
-        <v>147.079</v>
+        <v>147.021</v>
       </c>
       <c r="J1387" t="inlineStr">
         <is>
@@ -71500,7 +71500,7 @@
         </is>
       </c>
       <c r="K1387" t="n">
-        <v>0.04917038791320105</v>
+        <v>0.04875665187679212</v>
       </c>
       <c r="L1387" t="n">
         <v>77</v>
@@ -72568,7 +72568,7 @@
         <v>0</v>
       </c>
       <c r="I1408" t="n">
-        <v>122.312</v>
+        <v>121.442</v>
       </c>
       <c r="J1408" t="inlineStr">
         <is>
@@ -72576,10 +72576,10 @@
         </is>
       </c>
       <c r="K1408" t="n">
-        <v>0.03036021161168589</v>
+        <v>0.02303130370320439</v>
       </c>
       <c r="L1408" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1409">
@@ -73644,7 +73644,7 @@
         <v>0</v>
       </c>
       <c r="I1429" t="n">
-        <v>103.797</v>
+        <v>103.799</v>
       </c>
       <c r="J1429" t="inlineStr">
         <is>
@@ -73652,10 +73652,10 @@
         </is>
       </c>
       <c r="K1429" t="n">
-        <v>0.01308854532677439</v>
+        <v>0.01310806590146019</v>
       </c>
       <c r="L1429" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1430">
@@ -75796,7 +75796,7 @@
         <v>0</v>
       </c>
       <c r="I1471" t="n">
-        <v>127.806</v>
+        <v>127.803</v>
       </c>
       <c r="J1471" t="inlineStr">
         <is>
@@ -75804,10 +75804,10 @@
         </is>
       </c>
       <c r="K1471" t="n">
-        <v>0.050690562315028</v>
+        <v>0.0506658993752056</v>
       </c>
       <c r="L1471" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1472">
@@ -76872,7 +76872,7 @@
         <v>0</v>
       </c>
       <c r="I1492" t="n">
-        <v>130.821</v>
+        <v>130.8</v>
       </c>
       <c r="J1492" t="inlineStr">
         <is>
@@ -76880,10 +76880,10 @@
         </is>
       </c>
       <c r="K1492" t="n">
-        <v>0.03572192005320285</v>
+        <v>0.0355556611167851</v>
       </c>
       <c r="L1492" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1493">
@@ -77948,7 +77948,7 @@
         <v>0</v>
       </c>
       <c r="I1513" t="n">
-        <v>135.61</v>
+        <v>135.537</v>
       </c>
       <c r="J1513" t="inlineStr">
         <is>
@@ -77956,10 +77956,10 @@
         </is>
       </c>
       <c r="K1513" t="n">
-        <v>0.03929247488178533</v>
+        <v>0.03873301502877768</v>
       </c>
       <c r="L1513" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1514">
@@ -80100,7 +80100,7 @@
         <v>0</v>
       </c>
       <c r="I1555" t="n">
-        <v>111.999</v>
+        <v>112.014</v>
       </c>
       <c r="J1555" t="inlineStr">
         <is>
@@ -80108,7 +80108,7 @@
         </is>
       </c>
       <c r="K1555" t="n">
-        <v>0.01710014893385159</v>
+        <v>0.01723636892004787</v>
       </c>
       <c r="L1555" t="n">
         <v>42</v>
@@ -81176,7 +81176,7 @@
         <v>0</v>
       </c>
       <c r="I1576" t="n">
-        <v>37.107</v>
+        <v>37.108</v>
       </c>
       <c r="J1576" t="inlineStr">
         <is>
@@ -81184,7 +81184,7 @@
         </is>
       </c>
       <c r="K1576" t="n">
-        <v>-0.08598945760874921</v>
+        <v>-0.08596482585349041</v>
       </c>
       <c r="L1576" t="n">
         <v>1</v>
@@ -82252,7 +82252,7 @@
         <v>0</v>
       </c>
       <c r="I1597" t="n">
-        <v>79.105</v>
+        <v>79.101</v>
       </c>
       <c r="J1597" t="inlineStr">
         <is>
@@ -82260,7 +82260,7 @@
         </is>
       </c>
       <c r="K1597" t="n">
-        <v>-0.0262202252723579</v>
+        <v>-0.02626946513202433</v>
       </c>
       <c r="L1597" t="n">
         <v>9</v>
@@ -83339,7 +83339,7 @@
         <v>0.02576919386215137</v>
       </c>
       <c r="L1618" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1619">
@@ -84415,7 +84415,7 @@
         <v>0.04134172345406539</v>
       </c>
       <c r="L1639" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1640">
@@ -85480,7 +85480,7 @@
         <v>0</v>
       </c>
       <c r="I1660" t="n">
-        <v>131.238</v>
+        <v>131.236</v>
       </c>
       <c r="J1660" t="inlineStr">
         <is>
@@ -85488,7 +85488,7 @@
         </is>
       </c>
       <c r="K1660" t="n">
-        <v>0.0176170463533023</v>
+        <v>0.01760153838996303</v>
       </c>
       <c r="L1660" t="n">
         <v>43</v>
@@ -86556,7 +86556,7 @@
         <v>0</v>
       </c>
       <c r="I1681" t="n">
-        <v>133.498</v>
+        <v>133.226</v>
       </c>
       <c r="J1681" t="inlineStr">
         <is>
@@ -86564,10 +86564,10 @@
         </is>
       </c>
       <c r="K1681" t="n">
-        <v>0.05279013280338152</v>
+        <v>0.05064509006025042</v>
       </c>
       <c r="L1681" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1682">
@@ -88708,7 +88708,7 @@
         <v>0</v>
       </c>
       <c r="I1723" t="n">
-        <v>123.523</v>
+        <v>123.522</v>
       </c>
       <c r="J1723" t="inlineStr">
         <is>
@@ -88716,7 +88716,7 @@
         </is>
       </c>
       <c r="K1723" t="n">
-        <v>-0.004448922022969981</v>
+        <v>-0.004456981664315962</v>
       </c>
       <c r="L1723" t="n">
         <v>17</v>
@@ -89784,7 +89784,7 @@
         <v>0</v>
       </c>
       <c r="I1744" t="n">
-        <v>85.348</v>
+        <v>85.349</v>
       </c>
       <c r="J1744" t="inlineStr">
         <is>
@@ -89792,7 +89792,7 @@
         </is>
       </c>
       <c r="K1744" t="n">
-        <v>-0.07440705354141142</v>
+        <v>-0.07439620861304208</v>
       </c>
       <c r="L1744" t="n">
         <v>2</v>
@@ -90860,7 +90860,7 @@
         <v>0</v>
       </c>
       <c r="I1765" t="n">
-        <v>135.896</v>
+        <v>135.9</v>
       </c>
       <c r="J1765" t="inlineStr">
         <is>
@@ -90868,10 +90868,10 @@
         </is>
       </c>
       <c r="K1765" t="n">
-        <v>0.03228354830378444</v>
+        <v>0.03231393281983519</v>
       </c>
       <c r="L1765" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1766">
@@ -91936,7 +91936,7 @@
         <v>0</v>
       </c>
       <c r="I1786" t="n">
-        <v>71.69799999999999</v>
+        <v>71.69499999999999</v>
       </c>
       <c r="J1786" t="inlineStr">
         <is>
@@ -91944,10 +91944,10 @@
         </is>
       </c>
       <c r="K1786" t="n">
-        <v>-0.02007735727855464</v>
+        <v>-0.02011835936966133</v>
       </c>
       <c r="L1786" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1787">
@@ -93023,7 +93023,7 @@
         <v>0.01321148217434498</v>
       </c>
       <c r="L1807" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1808">
@@ -97316,7 +97316,7 @@
         <v>0</v>
       </c>
       <c r="I1891" t="n">
-        <v>110.189</v>
+        <v>110.218</v>
       </c>
       <c r="J1891" t="inlineStr">
         <is>
@@ -97324,7 +97324,7 @@
         </is>
       </c>
       <c r="K1891" t="n">
-        <v>-0.04934085654139497</v>
+        <v>-0.04909065810815472</v>
       </c>
       <c r="L1891" t="n">
         <v>3</v>
@@ -98392,7 +98392,7 @@
         <v>0</v>
       </c>
       <c r="I1912" t="n">
-        <v>136.577</v>
+        <v>136.573</v>
       </c>
       <c r="J1912" t="inlineStr">
         <is>
@@ -98400,10 +98400,10 @@
         </is>
       </c>
       <c r="K1912" t="n">
-        <v>0.04904295194789232</v>
+        <v>0.04901222809389205</v>
       </c>
       <c r="L1912" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1913">
